--- a/data/trans_dic/P79$alquiler_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P79$alquiler_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,64</t>
+          <t>1,33; 4,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,11</t>
+          <t>1,6; 3,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,81</t>
+          <t>1,71; 3,37</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,18</t>
+          <t>1,55; 2,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,1</t>
+          <t>1,99; 3,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,5</t>
+          <t>1,89; 3,08</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,38</t>
+          <t>0,33; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,7</t>
+          <t>0,46; 2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,57</t>
+          <t>0,58; 1,86</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,93</t>
+          <t>1,42; 2,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,59</t>
+          <t>1,86; 2,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,06</t>
+          <t>1,8; 2,52</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23075</t>
+          <t>32170</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3810; 17907</t>
+          <t>7311; 24504</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9572; 22258</t>
+          <t>12477; 26134</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15543; 34004</t>
+          <t>22774; 44868</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>102720</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21362; 48413</t>
+          <t>33392; 62494</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29933; 65189</t>
+          <t>41601; 78154</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61487; 108008</t>
+          <t>80541; 130744</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>14662</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1385; 15267</t>
+          <t>2356; 18456</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2017; 10950</t>
+          <t>3299; 14724</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4880; 20233</t>
+          <t>8233; 26419</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33376; 64919</t>
+          <t>48465; 83176</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49511; 89770</t>
+          <t>66732; 107204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90593; 140304</t>
+          <t>126050; 176738</t>
         </is>
       </c>
     </row>
